--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.89992983275467</v>
+        <v>3.071238597822633</v>
       </c>
       <c r="D2" t="n">
-        <v>19.2360114076133</v>
+        <v>3.125851853737161</v>
       </c>
       <c r="E2" t="n">
-        <v>3.666069074359658</v>
+        <v>0.5957362245834446</v>
       </c>
       <c r="F2" t="n">
-        <v>3.853991890479304</v>
+        <v>0.6262736822028868</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.39284382929028</v>
+        <v>1.85133712225967</v>
       </c>
       <c r="D3" t="n">
-        <v>11.7357103702094</v>
+        <v>1.907052935159028</v>
       </c>
       <c r="E3" t="n">
-        <v>3.666069074359658</v>
+        <v>0.5957362245834446</v>
       </c>
       <c r="F3" t="n">
-        <v>3.853991890479304</v>
+        <v>0.6262736822028868</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.87871464781357</v>
+        <v>1.767791130269704</v>
       </c>
       <c r="D4" t="n">
-        <v>10.5211097395888</v>
+        <v>1.70968033268318</v>
       </c>
       <c r="E4" t="n">
-        <v>3.666069074359658</v>
+        <v>0.5957362245834446</v>
       </c>
       <c r="F4" t="n">
-        <v>3.853991890479304</v>
+        <v>0.6262736822028868</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
